--- a/results/pooled_results_OR_multi_exposure_models_cold_mother.xlsx
+++ b/results/pooled_results_OR_multi_exposure_models_cold_mother.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CA26A4-C190-46FA-9824-5E25A7CDE81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A5868E-3833-4C80-AD40-BE29AB42709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{B34C9846-5C9E-4699-A4E5-B319E9F77E52}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
   <si>
     <t>OR</t>
   </si>
@@ -174,6 +174,12 @@
   <si>
     <t>Stomach ulcer</t>
   </si>
+  <si>
+    <t>Rheumatism</t>
+  </si>
+  <si>
+    <t>&lt;.0001</t>
+  </si>
 </sst>
 </file>
 
@@ -182,7 +188,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -315,12 +321,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -333,10 +337,14 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -672,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D0A0F0-8041-46B8-8B55-5A98C98C3474}">
-  <dimension ref="B1:V50"/>
+  <dimension ref="B1:V53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -775,7 +783,7 @@
       <c r="F7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H7"/>
@@ -788,7 +796,7 @@
       <c r="K7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="M7"/>
@@ -801,7 +809,7 @@
       <c r="P7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="R7"/>
@@ -814,7 +822,7 @@
       <c r="U7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="V7" s="17" t="s">
+      <c r="V7" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -863,55 +871,55 @@
         <v>8</v>
       </c>
       <c r="D9" s="1">
-        <v>1.2208848999999999</v>
+        <v>1.0149250000000001</v>
       </c>
       <c r="E9" s="1">
-        <v>0.75206799999999996</v>
+        <v>0.60242779999999996</v>
       </c>
       <c r="F9" s="1">
-        <v>1.9819483</v>
+        <v>1.7098693</v>
       </c>
       <c r="G9" s="2">
-        <v>0.419178</v>
+        <v>0.95558799999999999</v>
       </c>
       <c r="H9"/>
       <c r="I9" s="1">
-        <v>1.2884203999999999</v>
+        <v>1.0493307000000001</v>
       </c>
       <c r="J9" s="1">
-        <v>0.79726490000000005</v>
+        <v>0.62758829999999999</v>
       </c>
       <c r="K9" s="1">
-        <v>2.0821527</v>
+        <v>1.7544858999999999</v>
       </c>
       <c r="L9" s="2">
-        <v>0.30049100000000001</v>
+        <v>0.85426299999999999</v>
       </c>
       <c r="M9"/>
       <c r="N9" s="1">
-        <v>1.3058501</v>
+        <v>1.0601261</v>
       </c>
       <c r="O9" s="1">
-        <v>0.8078246</v>
+        <v>0.63210500000000003</v>
       </c>
       <c r="P9" s="1">
-        <v>2.1109092</v>
+        <v>1.7779758000000001</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.27588499999999999</v>
+        <v>0.82477999999999996</v>
       </c>
       <c r="R9"/>
       <c r="S9" s="1">
-        <v>1.3276196</v>
+        <v>1.0908357</v>
       </c>
       <c r="T9" s="1">
-        <v>0.7918655</v>
+        <v>0.63053420000000004</v>
       </c>
       <c r="U9" s="1">
-        <v>2.2258499999999999</v>
+        <v>1.8871656999999999</v>
       </c>
       <c r="V9" s="2">
-        <v>0.28204000000000001</v>
+        <v>0.75577899999999998</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -931,10 +939,10 @@
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="12"/>
+      <c r="E11" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="17"/>
       <c r="H11"/>
       <c r="M11"/>
       <c r="R11"/>
@@ -945,20 +953,32 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>1.2423246999999999</v>
+        <v>1.1444270999999999</v>
       </c>
       <c r="E12" s="1">
-        <v>0.76628110000000005</v>
+        <v>0.70052460000000005</v>
       </c>
       <c r="F12" s="1">
-        <v>2.0141051999999999</v>
+        <v>1.8696178999999999</v>
       </c>
       <c r="G12" s="2">
-        <v>0.37821199999999999</v>
+        <v>0.58979899999999996</v>
       </c>
       <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
       <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
       <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
@@ -966,20 +986,32 @@
         <v>2</v>
       </c>
       <c r="D13" s="9">
-        <v>1.9260946999999999</v>
+        <v>1.7883469999999999</v>
       </c>
       <c r="E13" s="9">
-        <v>1.1785304999999999</v>
+        <v>1.0796538</v>
       </c>
       <c r="F13" s="9">
-        <v>3.147853</v>
+        <v>2.9622318999999999</v>
       </c>
       <c r="G13" s="10">
-        <v>8.9359999999999995E-3</v>
+        <v>2.3986E-2</v>
       </c>
       <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
       <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
       <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
@@ -987,27 +1019,51 @@
         <v>3</v>
       </c>
       <c r="D14" s="9">
-        <v>3.3008818999999998</v>
+        <v>2.9770097999999998</v>
       </c>
       <c r="E14" s="9">
-        <v>1.8341273</v>
+        <v>1.6053896999999999</v>
       </c>
       <c r="F14" s="9">
-        <v>5.9406026000000001</v>
+        <v>5.5205209000000002</v>
       </c>
       <c r="G14" s="10">
-        <v>7.0500000000000006E-5</v>
+        <v>5.4900000000000001E-4</v>
       </c>
       <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
       <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
       <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="7"/>
       <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
       <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
       <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
@@ -1020,12 +1076,21 @@
       <c r="I16" s="1">
         <v>1</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K16" s="12"/>
+      <c r="J16" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16"/>
       <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
       <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
@@ -1034,19 +1099,27 @@
       </c>
       <c r="H17"/>
       <c r="I17" s="1">
-        <v>1.3495313</v>
+        <v>1.457058</v>
       </c>
       <c r="J17" s="1">
-        <v>0.89845620000000004</v>
+        <v>0.95670379999999999</v>
       </c>
       <c r="K17" s="1">
-        <v>2.0270711000000001</v>
+        <v>2.2190965999999999</v>
       </c>
       <c r="L17" s="2">
-        <v>0.14863399999999999</v>
+        <v>7.9450999999999994E-2</v>
       </c>
       <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
       <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
@@ -1055,26 +1128,46 @@
       </c>
       <c r="H18"/>
       <c r="I18" s="1">
-        <v>1.5229257</v>
+        <v>1.6389488999999999</v>
       </c>
       <c r="J18" s="1">
-        <v>0.89574069999999995</v>
+        <v>0.94722759999999995</v>
       </c>
       <c r="K18" s="1">
-        <v>2.5892567</v>
+        <v>2.8358059</v>
       </c>
       <c r="L18" s="2">
-        <v>0.120228</v>
+        <v>7.7332999999999999E-2</v>
       </c>
       <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
       <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
       <c r="C19" s="7"/>
       <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
       <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
       <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
@@ -1084,15 +1177,24 @@
         <v>0</v>
       </c>
       <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
       <c r="M20"/>
       <c r="N20" s="1">
         <v>1</v>
       </c>
-      <c r="O20" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="12"/>
+      <c r="O20" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="17"/>
+      <c r="Q20"/>
       <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
@@ -1100,20 +1202,28 @@
         <v>1</v>
       </c>
       <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
       <c r="M21"/>
-      <c r="N21" s="9">
-        <v>1.8742858</v>
-      </c>
-      <c r="O21" s="9">
-        <v>1.0463164</v>
-      </c>
-      <c r="P21" s="9">
-        <v>3.3574423000000002</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>3.4696999999999999E-2</v>
+      <c r="N21" s="1">
+        <v>1.6748396000000001</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0.92860810000000005</v>
+      </c>
+      <c r="P21" s="1">
+        <v>3.0207442000000002</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>8.6499999999999994E-2</v>
       </c>
       <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
@@ -1121,20 +1231,28 @@
         <v>2</v>
       </c>
       <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
       <c r="M22"/>
       <c r="N22" s="9">
-        <v>2.4292251</v>
+        <v>2.2698412000000001</v>
       </c>
       <c r="O22" s="9">
-        <v>1.2835599</v>
+        <v>1.2159321000000001</v>
       </c>
       <c r="P22" s="9">
-        <v>4.5974750999999996</v>
+        <v>4.2372259000000003</v>
       </c>
       <c r="Q22" s="10">
-        <v>6.4559999999999999E-3</v>
+        <v>1.009E-2</v>
       </c>
       <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
@@ -1142,27 +1260,47 @@
         <v>3</v>
       </c>
       <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
       <c r="M23"/>
       <c r="N23" s="9">
-        <v>3.0696262999999999</v>
+        <v>2.6073051999999999</v>
       </c>
       <c r="O23" s="9">
-        <v>1.2787147999999999</v>
+        <v>1.0456091000000001</v>
       </c>
       <c r="P23" s="9">
-        <v>7.3688098000000002</v>
+        <v>6.5015121999999996</v>
       </c>
       <c r="Q23" s="10">
-        <v>1.2111E-2</v>
+        <v>3.9829999999999997E-2</v>
       </c>
       <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="7"/>
       <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
       <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
       <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
@@ -1172,15 +1310,24 @@
         <v>18</v>
       </c>
       <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
       <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
       <c r="R25"/>
       <c r="S25" s="1">
         <v>1</v>
       </c>
-      <c r="T25" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="U25" s="12"/>
+      <c r="T25" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U25" s="17"/>
+      <c r="V25"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
@@ -1188,19 +1335,27 @@
         <v>19</v>
       </c>
       <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
       <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
       <c r="R26"/>
       <c r="S26" s="1">
-        <v>0.9034006</v>
+        <v>0.93529839999999997</v>
       </c>
       <c r="T26" s="1">
-        <v>0.50392420000000004</v>
+        <v>0.5128144</v>
       </c>
       <c r="U26" s="1">
-        <v>1.6195550000000001</v>
+        <v>1.7058475</v>
       </c>
       <c r="V26" s="2">
-        <v>0.73280000000000001</v>
+        <v>0.82711599999999996</v>
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
@@ -1209,19 +1364,27 @@
         <v>20</v>
       </c>
       <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
       <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
       <c r="R27"/>
       <c r="S27" s="1">
-        <v>1.1677367000000001</v>
+        <v>1.2019877000000001</v>
       </c>
       <c r="T27" s="1">
-        <v>0.68637340000000002</v>
+        <v>0.70160460000000002</v>
       </c>
       <c r="U27" s="1">
-        <v>1.9866870000000001</v>
+        <v>2.0592432000000001</v>
       </c>
       <c r="V27" s="2">
-        <v>0.56705000000000005</v>
+        <v>0.50280400000000003</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -1230,26 +1393,42 @@
         <v>21</v>
       </c>
       <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
       <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
       <c r="R28"/>
       <c r="S28" s="1">
-        <v>1.1427974000000001</v>
+        <v>0.96410149999999994</v>
       </c>
       <c r="T28" s="1">
-        <v>0.6429918</v>
+        <v>0.51869980000000004</v>
       </c>
       <c r="U28" s="1">
-        <v>2.0311080000000001</v>
+        <v>1.7919647000000001</v>
       </c>
       <c r="V28" s="2">
-        <v>0.64885999999999999</v>
+        <v>0.90787499999999999</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
       <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
       <c r="R29"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -1258,119 +1437,135 @@
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="9">
-        <v>0.96876530000000005</v>
+        <v>0.95905010000000002</v>
       </c>
       <c r="E30" s="9">
-        <v>0.95070619999999995</v>
+        <v>0.93926319999999996</v>
       </c>
       <c r="F30" s="9">
-        <v>0.98716729999999997</v>
+        <v>0.97925390000000001</v>
       </c>
       <c r="G30" s="10">
-        <v>9.5600000000000004E-4</v>
+        <v>8.6199999999999995E-5</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="9">
-        <v>0.97025189999999994</v>
+        <v>0.96089089999999999</v>
       </c>
       <c r="J30" s="9">
-        <v>0.9521056</v>
+        <v>0.94092730000000002</v>
       </c>
       <c r="K30" s="9">
-        <v>0.98874410000000001</v>
+        <v>0.98127810000000004</v>
       </c>
       <c r="L30" s="10">
-        <v>1.727E-3</v>
+        <v>1.9900000000000001E-4</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="9">
-        <v>0.96606499999999995</v>
+        <v>0.95613950000000003</v>
       </c>
       <c r="O30" s="9">
-        <v>0.94821820000000001</v>
+        <v>0.9365388</v>
       </c>
       <c r="P30" s="9">
-        <v>0.98424769999999995</v>
+        <v>0.97615039999999997</v>
       </c>
       <c r="Q30" s="10">
-        <v>2.8800000000000001E-4</v>
+        <v>2.2500000000000001E-5</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="9">
-        <v>0.97008349999999999</v>
+        <v>0.96079460000000005</v>
       </c>
       <c r="T30" s="9">
-        <v>0.95154519999999998</v>
+        <v>0.94051300000000004</v>
       </c>
       <c r="U30" s="9">
-        <v>0.98898299999999995</v>
+        <v>0.98151359999999999</v>
       </c>
       <c r="V30" s="10">
-        <v>2.0400000000000001E-3</v>
+        <v>2.42E-4</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="H31"/>
-      <c r="M31"/>
-      <c r="R31"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="10"/>
     </row>
     <row r="32" spans="2:22" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B32" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C32" s="5"/>
-      <c r="D32" s="1">
-        <v>0.95146730000000002</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0.90523160000000003</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1.0000644999999999</v>
-      </c>
-      <c r="G32" s="2">
-        <v>5.0297000000000001E-2</v>
-      </c>
-      <c r="H32"/>
-      <c r="I32" s="1">
-        <v>0.95598989999999995</v>
-      </c>
-      <c r="J32" s="1">
-        <v>0.90947829999999996</v>
-      </c>
-      <c r="K32" s="1">
-        <v>1.0048801999999999</v>
-      </c>
-      <c r="L32" s="2">
-        <v>7.6920000000000002E-2</v>
-      </c>
-      <c r="M32"/>
-      <c r="N32" s="1">
-        <v>0.95493819999999996</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0.90771740000000001</v>
-      </c>
-      <c r="P32" s="1">
-        <v>1.0046155000000001</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>7.4716000000000005E-2</v>
-      </c>
-      <c r="R32"/>
-      <c r="S32" s="1">
-        <v>0.96804829999999997</v>
-      </c>
-      <c r="T32" s="1">
-        <v>0.91955019999999998</v>
-      </c>
-      <c r="U32" s="1">
-        <v>1.019104</v>
-      </c>
-      <c r="V32" s="2">
-        <v>0.21543999999999999</v>
+      <c r="D32" s="9">
+        <v>0.93965359999999998</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.89086960000000004</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0.99110900000000002</v>
+      </c>
+      <c r="G32" s="10">
+        <v>2.2179000000000001E-2</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="9">
+        <v>0.94358560000000002</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0.89440889999999995</v>
+      </c>
+      <c r="K32" s="9">
+        <v>0.99546630000000003</v>
+      </c>
+      <c r="L32" s="10">
+        <v>3.3512E-2</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="9">
+        <v>0.94273580000000001</v>
+      </c>
+      <c r="O32" s="9">
+        <v>0.89313869999999995</v>
+      </c>
+      <c r="P32" s="9">
+        <v>0.99508700000000005</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>3.2509999999999997E-2</v>
+      </c>
+      <c r="R32" s="5"/>
+      <c r="S32" s="18">
+        <v>0.95651249999999999</v>
+      </c>
+      <c r="T32" s="18">
+        <v>0.90460810000000003</v>
+      </c>
+      <c r="U32" s="18">
+        <v>1.011395</v>
+      </c>
+      <c r="V32" s="19">
+        <v>0.118104</v>
       </c>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.3">
@@ -1390,34 +1585,34 @@
       <c r="D34" s="1">
         <v>1</v>
       </c>
-      <c r="E34" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="12"/>
+      <c r="E34" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="17"/>
       <c r="H34"/>
       <c r="I34" s="1">
         <v>1</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K34" s="12"/>
+      <c r="J34" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K34" s="17"/>
       <c r="M34"/>
       <c r="N34" s="1">
         <v>1</v>
       </c>
-      <c r="O34" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="P34" s="12"/>
+      <c r="O34" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P34" s="17"/>
       <c r="R34"/>
       <c r="S34" s="1">
         <v>1</v>
       </c>
-      <c r="T34" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="U34" s="12"/>
+      <c r="T34" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U34" s="17"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B35" s="5"/>
@@ -1425,55 +1620,55 @@
         <v>26</v>
       </c>
       <c r="D35" s="1">
-        <v>1.4361477</v>
+        <v>1.4101622</v>
       </c>
       <c r="E35" s="1">
-        <v>0.86532549999999997</v>
+        <v>0.834561</v>
       </c>
       <c r="F35" s="1">
-        <v>2.3835196999999999</v>
+        <v>2.3827587000000001</v>
       </c>
       <c r="G35" s="2">
-        <v>0.16133900000000001</v>
+        <v>0.19896900000000001</v>
       </c>
       <c r="H35"/>
       <c r="I35" s="1">
-        <v>1.3019959000000001</v>
+        <v>1.2878244000000001</v>
       </c>
       <c r="J35" s="1">
-        <v>0.78966409999999998</v>
+        <v>0.76763780000000004</v>
       </c>
       <c r="K35" s="1">
-        <v>2.1467269</v>
+        <v>2.1605132</v>
       </c>
       <c r="L35" s="2">
-        <v>0.300846</v>
+        <v>0.33781499999999998</v>
       </c>
       <c r="M35"/>
       <c r="N35" s="1">
-        <v>1.398217</v>
+        <v>1.3681528999999999</v>
       </c>
       <c r="O35" s="1">
-        <v>0.84644790000000003</v>
+        <v>0.81335679999999999</v>
       </c>
       <c r="P35" s="1">
-        <v>2.3096646999999999</v>
+        <v>2.3013789</v>
       </c>
       <c r="Q35" s="2">
-        <v>0.19046399999999999</v>
+        <v>0.23734</v>
       </c>
       <c r="R35"/>
       <c r="S35" s="1">
-        <v>1.4076580000000001</v>
+        <v>1.3708906000000001</v>
       </c>
       <c r="T35" s="1">
-        <v>0.81863490000000005</v>
+        <v>0.78853050000000002</v>
       </c>
       <c r="U35" s="1">
-        <v>2.4204940000000001</v>
+        <v>2.3833460999999998</v>
       </c>
       <c r="V35" s="2">
-        <v>0.21621000000000001</v>
+        <v>0.26345299999999999</v>
       </c>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.3">
@@ -1482,55 +1677,55 @@
         <v>27</v>
       </c>
       <c r="D36" s="1">
-        <v>1.4553627</v>
+        <v>1.4622040000000001</v>
       </c>
       <c r="E36" s="1">
-        <v>0.8174091</v>
+        <v>0.80322930000000003</v>
       </c>
       <c r="F36" s="1">
-        <v>2.5912120999999999</v>
+        <v>2.6618059999999999</v>
       </c>
       <c r="G36" s="2">
-        <v>0.202233</v>
+        <v>0.21374099999999999</v>
       </c>
       <c r="H36"/>
       <c r="I36" s="1">
-        <v>1.2219333999999999</v>
+        <v>1.2439344999999999</v>
       </c>
       <c r="J36" s="1">
-        <v>0.69321900000000003</v>
+        <v>0.69054570000000004</v>
       </c>
       <c r="K36" s="1">
-        <v>2.1538954000000001</v>
+        <v>2.2407976000000001</v>
       </c>
       <c r="L36" s="2">
-        <v>0.48815500000000001</v>
+        <v>0.46715000000000001</v>
       </c>
       <c r="M36"/>
       <c r="N36" s="1">
-        <v>1.4414605</v>
+        <v>1.4274985</v>
       </c>
       <c r="O36" s="1">
-        <v>0.81172060000000001</v>
+        <v>0.78663870000000002</v>
       </c>
       <c r="P36" s="1">
-        <v>2.5597582999999999</v>
+        <v>2.5904546000000002</v>
       </c>
       <c r="Q36" s="2">
-        <v>0.21193799999999999</v>
+        <v>0.24163000000000001</v>
       </c>
       <c r="R36"/>
       <c r="S36" s="1">
-        <v>1.2955686</v>
+        <v>1.3098882000000001</v>
       </c>
       <c r="T36" s="1">
-        <v>0.70236010000000004</v>
+        <v>0.70146180000000002</v>
       </c>
       <c r="U36" s="1">
-        <v>2.3897970000000002</v>
+        <v>2.4460448000000001</v>
       </c>
       <c r="V36" s="2">
-        <v>0.40694000000000002</v>
+        <v>0.39675899999999997</v>
       </c>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.3">
@@ -1550,34 +1745,34 @@
       <c r="D38" s="1">
         <v>1</v>
       </c>
-      <c r="E38" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="12"/>
+      <c r="E38" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" s="17"/>
       <c r="H38"/>
       <c r="I38" s="1">
         <v>1</v>
       </c>
-      <c r="J38" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K38" s="12"/>
+      <c r="J38" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="17"/>
       <c r="M38"/>
       <c r="N38" s="1">
         <v>1</v>
       </c>
-      <c r="O38" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="P38" s="12"/>
+      <c r="O38" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P38" s="17"/>
       <c r="R38"/>
       <c r="S38" s="1">
         <v>1</v>
       </c>
-      <c r="T38" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="U38" s="12"/>
+      <c r="T38" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U38" s="17"/>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="5"/>
@@ -1585,55 +1780,55 @@
         <v>8</v>
       </c>
       <c r="D39" s="1">
-        <v>0.76208589999999998</v>
+        <v>0.74532310000000002</v>
       </c>
       <c r="E39" s="1">
-        <v>0.51357180000000002</v>
+        <v>0.50237140000000002</v>
       </c>
       <c r="F39" s="1">
-        <v>1.1308545999999999</v>
+        <v>1.1057684000000001</v>
       </c>
       <c r="G39" s="2">
-        <v>0.17696799999999999</v>
+        <v>0.144094</v>
       </c>
       <c r="H39"/>
       <c r="I39" s="1">
-        <v>0.80048059999999999</v>
+        <v>0.78334380000000003</v>
       </c>
       <c r="J39" s="1">
-        <v>0.54109779999999996</v>
+        <v>0.52883190000000002</v>
       </c>
       <c r="K39" s="1">
-        <v>1.1842022000000001</v>
+        <v>1.160345</v>
       </c>
       <c r="L39" s="2">
-        <v>0.26497500000000002</v>
+        <v>0.223055</v>
       </c>
       <c r="M39"/>
       <c r="N39" s="1">
-        <v>0.80760580000000004</v>
+        <v>0.79150319999999996</v>
       </c>
       <c r="O39" s="1">
-        <v>0.54654599999999998</v>
+        <v>0.5341359</v>
       </c>
       <c r="P39" s="1">
-        <v>1.1933619</v>
+        <v>1.1728801</v>
       </c>
       <c r="Q39" s="2">
-        <v>0.283078</v>
+        <v>0.24376999999999999</v>
       </c>
       <c r="R39"/>
       <c r="S39" s="1">
-        <v>0.84920399999999996</v>
+        <v>0.84351140000000002</v>
       </c>
       <c r="T39" s="1">
-        <v>0.55895280000000003</v>
+        <v>0.55819819999999998</v>
       </c>
       <c r="U39" s="1">
-        <v>1.290176</v>
+        <v>1.2746575</v>
       </c>
       <c r="V39" s="2">
-        <v>0.44292999999999999</v>
+        <v>0.41893399999999997</v>
       </c>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.3">
@@ -1653,152 +1848,150 @@
       <c r="D41" s="1">
         <v>1</v>
       </c>
-      <c r="E41" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" s="12"/>
+      <c r="E41" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="17"/>
       <c r="H41"/>
       <c r="I41" s="1">
         <v>1</v>
       </c>
-      <c r="J41" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K41" s="12"/>
+      <c r="J41" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="17"/>
       <c r="M41"/>
       <c r="N41" s="1">
         <v>1</v>
       </c>
-      <c r="O41" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="P41" s="12"/>
+      <c r="O41" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="17"/>
       <c r="R41"/>
       <c r="S41" s="1">
         <v>1</v>
       </c>
-      <c r="T41" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="U41" s="12"/>
+      <c r="T41" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U41" s="17"/>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B42" s="18"/>
-      <c r="C42" s="18" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="1">
-        <v>1.2324128000000001</v>
+        <v>1.1312201</v>
       </c>
       <c r="E42" s="1">
-        <v>0.54318889999999997</v>
+        <v>0.49574010000000002</v>
       </c>
       <c r="F42" s="1">
-        <v>2.7961567999999999</v>
+        <v>2.5813103000000002</v>
       </c>
       <c r="G42" s="2">
-        <v>0.61701700000000004</v>
+        <v>0.76950700000000005</v>
       </c>
       <c r="H42"/>
       <c r="I42" s="1">
-        <v>1.1214280000000001</v>
+        <v>1.0456687</v>
       </c>
       <c r="J42" s="1">
-        <v>0.49703160000000002</v>
+        <v>0.45987040000000001</v>
       </c>
       <c r="K42" s="1">
-        <v>2.5302229999999999</v>
+        <v>2.3776763000000001</v>
       </c>
       <c r="L42" s="2">
-        <v>0.78244800000000003</v>
+        <v>0.91511799999999999</v>
       </c>
       <c r="M42"/>
       <c r="N42" s="1">
-        <v>1.1294401999999999</v>
+        <v>1.0809732000000001</v>
       </c>
       <c r="O42" s="1">
-        <v>0.50045360000000005</v>
+        <v>0.47492380000000001</v>
       </c>
       <c r="P42" s="1">
-        <v>2.5489576</v>
+        <v>2.4604013999999998</v>
       </c>
       <c r="Q42" s="2">
-        <v>0.76937699999999998</v>
+        <v>0.85275000000000001</v>
       </c>
       <c r="R42"/>
       <c r="S42" s="1">
-        <v>1.1739272999999999</v>
+        <v>1.1442859999999999</v>
       </c>
       <c r="T42" s="1">
-        <v>0.49086079999999999</v>
+        <v>0.4743233</v>
       </c>
       <c r="U42" s="1">
-        <v>2.807528</v>
+        <v>2.7605442</v>
       </c>
       <c r="V42" s="2">
-        <v>0.71841999999999995</v>
+        <v>0.76411600000000002</v>
       </c>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B43" s="18"/>
-      <c r="C43" s="18" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D43" s="1">
-        <v>1.4472582000000001</v>
+        <v>1.4833453999999999</v>
       </c>
       <c r="E43" s="1">
-        <v>0.54956300000000002</v>
+        <v>0.55492470000000005</v>
       </c>
       <c r="F43" s="1">
-        <v>3.811312</v>
+        <v>3.9650672999999999</v>
       </c>
       <c r="G43" s="2">
-        <v>0.454179</v>
+        <v>0.43173099999999998</v>
       </c>
       <c r="H43"/>
       <c r="I43" s="1">
-        <v>1.4599784</v>
+        <v>1.5148146</v>
       </c>
       <c r="J43" s="1">
-        <v>0.55697140000000001</v>
+        <v>0.56827780000000006</v>
       </c>
       <c r="K43" s="1">
-        <v>3.8270130999999998</v>
+        <v>4.0379253000000004</v>
       </c>
       <c r="L43" s="2">
-        <v>0.44137799999999999</v>
+        <v>0.40628999999999998</v>
       </c>
       <c r="M43"/>
       <c r="N43" s="1">
-        <v>1.5085189999999999</v>
+        <v>1.5847452</v>
       </c>
       <c r="O43" s="1">
-        <v>0.57486009999999998</v>
+        <v>0.59387990000000002</v>
       </c>
       <c r="P43" s="1">
-        <v>3.9585796000000002</v>
+        <v>4.2288302</v>
       </c>
       <c r="Q43" s="2">
-        <v>0.40346300000000002</v>
+        <v>0.35774</v>
       </c>
       <c r="R43"/>
       <c r="S43" s="1">
-        <v>1.793507</v>
+        <v>1.9199379999999999</v>
       </c>
       <c r="T43" s="1">
-        <v>0.65188880000000005</v>
+        <v>0.68734320000000004</v>
       </c>
       <c r="U43" s="1">
-        <v>4.93438</v>
+        <v>5.3629135999999997</v>
       </c>
       <c r="V43" s="2">
-        <v>0.25780999999999998</v>
+        <v>0.213175</v>
       </c>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B44" s="19"/>
-      <c r="C44" s="20"/>
       <c r="H44"/>
       <c r="M44"/>
       <c r="R44"/>
@@ -1813,34 +2006,34 @@
       <c r="D45" s="1">
         <v>1</v>
       </c>
-      <c r="E45" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="12"/>
+      <c r="E45" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="17"/>
       <c r="H45"/>
       <c r="I45" s="1">
         <v>1</v>
       </c>
-      <c r="J45" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="12"/>
+      <c r="J45" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="17"/>
       <c r="M45"/>
       <c r="N45" s="1">
         <v>1</v>
       </c>
-      <c r="O45" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="12"/>
+      <c r="O45" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="17"/>
       <c r="R45"/>
       <c r="S45" s="1">
         <v>1</v>
       </c>
-      <c r="T45" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="U45" s="12"/>
+      <c r="T45" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U45" s="17"/>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B46" s="5"/>
@@ -1848,55 +2041,55 @@
         <v>39</v>
       </c>
       <c r="D46" s="9">
-        <v>2.3932704</v>
+        <v>2.3250188000000001</v>
       </c>
       <c r="E46" s="9">
-        <v>1.4679180999999999</v>
+        <v>1.3937153</v>
       </c>
       <c r="F46" s="9">
-        <v>3.9019501000000001</v>
+        <v>3.8786347999999999</v>
       </c>
       <c r="G46" s="10">
-        <v>4.7199999999999998E-4</v>
+        <v>1.242E-3</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="9">
-        <v>2.3581557000000002</v>
+        <v>2.2731731000000002</v>
       </c>
       <c r="J46" s="9">
-        <v>1.4534114</v>
+        <v>1.3648506</v>
       </c>
       <c r="K46" s="9">
-        <v>3.8261007</v>
+        <v>3.7859938</v>
       </c>
       <c r="L46" s="10">
-        <v>5.1800000000000001E-4</v>
+        <v>1.6180000000000001E-3</v>
       </c>
       <c r="M46" s="5"/>
       <c r="N46" s="9">
-        <v>2.4406525999999999</v>
+        <v>2.3441681000000001</v>
       </c>
       <c r="O46" s="9">
-        <v>1.5041042</v>
+        <v>1.408096</v>
       </c>
       <c r="P46" s="9">
-        <v>3.9603538999999999</v>
+        <v>3.9025211</v>
       </c>
       <c r="Q46" s="10">
-        <v>3.0699999999999998E-4</v>
+        <v>1.06E-3</v>
       </c>
       <c r="R46" s="5"/>
       <c r="S46" s="9">
-        <v>2.1172054</v>
+        <v>1.9712489</v>
       </c>
       <c r="T46" s="9">
-        <v>1.2537122000000001</v>
+        <v>1.1319851000000001</v>
       </c>
       <c r="U46" s="9">
-        <v>3.5754290000000002</v>
+        <v>3.4327502000000001</v>
       </c>
       <c r="V46" s="10">
-        <v>5.0400000000000002E-3</v>
+        <v>1.6514000000000001E-2</v>
       </c>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.3">
@@ -1916,99 +2109,206 @@
       <c r="D48" s="1">
         <v>1</v>
       </c>
-      <c r="E48" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="12"/>
+      <c r="E48" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="17"/>
       <c r="H48"/>
       <c r="I48" s="1">
         <v>1</v>
       </c>
-      <c r="J48" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="12"/>
+      <c r="J48" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="17"/>
       <c r="M48"/>
       <c r="N48" s="1">
         <v>1</v>
       </c>
-      <c r="O48" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="12"/>
+      <c r="O48" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="17"/>
       <c r="R48"/>
       <c r="S48" s="1">
         <v>1</v>
       </c>
-      <c r="T48" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="U48" s="12"/>
-    </row>
-    <row r="49" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="6"/>
-      <c r="C49" s="3" t="s">
+      <c r="T48" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U48" s="17"/>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B49" s="5"/>
+      <c r="C49" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="3">
-        <v>1.8428791</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1.0398917000000001</v>
-      </c>
-      <c r="F49" s="3">
-        <v>3.2659204000000002</v>
-      </c>
-      <c r="G49" s="17">
-        <v>3.6283000000000003E-2</v>
-      </c>
-      <c r="H49" s="6"/>
-      <c r="I49" s="3">
-        <v>1.9358506</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1.0959228000000001</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3.4195088</v>
-      </c>
-      <c r="L49" s="17">
-        <v>2.2911000000000001E-2</v>
-      </c>
-      <c r="M49" s="6"/>
-      <c r="N49" s="3">
-        <v>1.9059493000000001</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1.0751930999999999</v>
-      </c>
-      <c r="P49" s="3">
-        <v>3.3785957999999998</v>
-      </c>
-      <c r="Q49" s="17">
-        <v>2.7264E-2</v>
-      </c>
-      <c r="R49" s="6"/>
-      <c r="S49" s="3">
-        <v>1.8639534</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1.0156257</v>
-      </c>
-      <c r="U49" s="3">
-        <v>3.4208690000000002</v>
-      </c>
-      <c r="V49" s="17">
-        <v>4.444E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D49" s="1">
+        <v>1.5979749999999999</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.88358009999999998</v>
+      </c>
+      <c r="F49" s="1">
+        <v>2.8899748000000001</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0.120946</v>
+      </c>
+      <c r="H49"/>
+      <c r="I49" s="1">
+        <v>1.6547065999999999</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0.91747630000000002</v>
+      </c>
+      <c r="K49" s="1">
+        <v>2.9843321</v>
+      </c>
+      <c r="L49" s="2">
+        <v>9.4140000000000001E-2</v>
+      </c>
+      <c r="M49"/>
+      <c r="N49" s="1">
+        <v>1.6701292999999999</v>
+      </c>
+      <c r="O49" s="1">
+        <v>0.92466139999999997</v>
+      </c>
+      <c r="P49" s="1">
+        <v>3.0165980000000001</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>8.9029999999999998E-2</v>
+      </c>
+      <c r="R49"/>
+      <c r="S49" s="1">
+        <v>1.6705832</v>
+      </c>
+      <c r="T49" s="1">
+        <v>0.89314819999999995</v>
+      </c>
+      <c r="U49" s="1">
+        <v>3.1247316000000001</v>
+      </c>
+      <c r="V49" s="2">
+        <v>0.10814799999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B50" s="5"/>
+      <c r="C50" s="9"/>
+      <c r="H50"/>
+      <c r="M50"/>
+      <c r="R50"/>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B51" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" s="17"/>
+      <c r="H51"/>
+      <c r="I51" s="1">
+        <v>1</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K51" s="17"/>
+      <c r="M51"/>
+      <c r="N51" s="1">
+        <v>1</v>
+      </c>
+      <c r="O51" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P51" s="17"/>
+      <c r="R51"/>
+      <c r="S51" s="1">
+        <v>1</v>
+      </c>
+      <c r="T51" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U51" s="17"/>
+    </row>
+    <row r="52" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="6"/>
+      <c r="C52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3">
+        <v>3.1884260000000002</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2.0249258999999999</v>
+      </c>
+      <c r="F52" s="3">
+        <v>5.0204605000000004</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="3">
+        <v>3.3045099000000002</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2.1052998999999999</v>
+      </c>
+      <c r="K52" s="3">
+        <v>5.1868075999999999</v>
+      </c>
+      <c r="L52" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="M52" s="6"/>
+      <c r="N52" s="3">
+        <v>3.2837168000000001</v>
+      </c>
+      <c r="O52" s="3">
+        <v>2.0940528999999999</v>
+      </c>
+      <c r="P52" s="3">
+        <v>5.1492471999999996</v>
+      </c>
+      <c r="Q52" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="R52" s="6"/>
+      <c r="S52" s="3">
+        <v>3.1215388000000002</v>
+      </c>
+      <c r="T52" s="3">
+        <v>1.9514213</v>
+      </c>
+      <c r="U52" s="3">
+        <v>4.9932860000000003</v>
+      </c>
+      <c r="V52" s="20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="36">
     <mergeCell ref="E45:F45"/>
     <mergeCell ref="J45:K45"/>
     <mergeCell ref="O45:P45"/>
     <mergeCell ref="T45:U45"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="O51:P51"/>
+    <mergeCell ref="T51:U51"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="J48:K48"/>
     <mergeCell ref="O48:P48"/>
@@ -2018,6 +2318,9 @@
     <mergeCell ref="O34:P34"/>
     <mergeCell ref="T34:U34"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="T25:U25"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="O38:P38"/>
@@ -2026,9 +2329,6 @@
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="O41:P41"/>
     <mergeCell ref="T41:U41"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="T25:U25"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="I5:L5"/>
     <mergeCell ref="N5:Q5"/>
